--- a/shows/convergence-zone/playlists/analysis/cz-missing-spins.xlsx
+++ b/shows/convergence-zone/playlists/analysis/cz-missing-spins.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Add missing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remove or replace" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Add missing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Remove or replace" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Add missing'!$A$4:$I$134</definedName>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I134"/>
+  <dimension ref="A1:L134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -516,20 +516,35 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
+          <t>Release</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Where it fits</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Sheet row</t>
         </is>
@@ -566,17 +581,20 @@
           <t>2016</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>tight fit — may not have aired</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>before first logged spin (20:38)</t>
         </is>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="L5" s="5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -607,17 +625,20 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>tight fit — may not have aired</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>before first logged spin (20:38)</t>
         </is>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="L6" s="5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -648,17 +669,20 @@
           <t>2002</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>log gap 20:52–21:03 (11 min)</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="L7" s="2" t="n">
         <v>10</v>
       </c>
     </row>
@@ -689,17 +713,20 @@
           <t>1968</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>log gap 21:09–21:28 (20 min)</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="L8" s="2" t="n">
         <v>13</v>
       </c>
     </row>
@@ -720,25 +747,30 @@
           <t>Murmerations</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
-        <v/>
-      </c>
+      <c r="E9" s="2" t="n"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>log gap 21:09–21:28 (20 min)</t>
         </is>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="L9" s="2" t="n">
         <v>14</v>
       </c>
     </row>
@@ -759,23 +791,22 @@
           <t>Trio</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>log gap 21:09–21:28 (20 min)</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="L10" s="2" t="n">
         <v>15</v>
       </c>
     </row>
@@ -806,17 +837,20 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>log gap 21:33–21:44 (11 min)</t>
         </is>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="L11" s="2" t="n">
         <v>18</v>
       </c>
     </row>
@@ -847,17 +881,20 @@
           <t>1998</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>tight fit — may not have aired</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>log gap 21:56–22:01 (5 min)</t>
         </is>
       </c>
-      <c r="I12" s="5" t="n">
+      <c r="L12" s="5" t="n">
         <v>22</v>
       </c>
     </row>
@@ -892,17 +929,24 @@
           <t>1987</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Windham Hill Records</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>log gap 21:18–21:32 (14 min)</t>
         </is>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="L13" s="2" t="n">
         <v>13</v>
       </c>
     </row>
@@ -933,17 +977,24 @@
           <t>2016</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Just Music</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>log gap 21:18–21:32 (14 min)</t>
         </is>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="L14" s="2" t="n">
         <v>14</v>
       </c>
     </row>
@@ -974,17 +1025,28 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>WEATNU Records</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>tight fit — may not have aired</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>log gap 21:32–21:36 (4 min)</t>
         </is>
       </c>
-      <c r="I15" s="5" t="n">
+      <c r="L15" s="5" t="n">
         <v>16</v>
       </c>
     </row>
@@ -1015,17 +1077,24 @@
           <t>2002</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Soundcolours Gmbh</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>log gap 21:36–21:55 (19 min)</t>
         </is>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="L16" s="2" t="n">
         <v>18</v>
       </c>
     </row>
@@ -1056,17 +1125,28 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>N/A (Bandcamp)</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>log gap 21:36–21:55 (19 min)</t>
         </is>
       </c>
-      <c r="I17" s="2" t="n">
+      <c r="L17" s="2" t="n">
         <v>19</v>
       </c>
     </row>
@@ -1101,17 +1181,24 @@
           <t>2009</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Parlophone</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>tight fit — may not have aired</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>before first logged spin (20:35)</t>
         </is>
       </c>
-      <c r="I18" s="5" t="n">
+      <c r="L18" s="5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1142,17 +1229,24 @@
           <t>2016</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Holy Are You Recordings</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>log gap 20:45–20:58 (13 min)</t>
         </is>
       </c>
-      <c r="I19" s="2" t="n">
+      <c r="L19" s="2" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1183,17 +1277,24 @@
           <t>1999</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Earthtone Records</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>log gap 21:16–21:25 (9 min)</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="L20" s="2" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1224,17 +1325,24 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Synphaera Records</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>log gap 21:57–22:11 (14 min)</t>
         </is>
       </c>
-      <c r="I21" s="2" t="n">
+      <c r="L21" s="2" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1266,17 +1374,28 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Past Inside the Present</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>after last logged spin (22:15)</t>
         </is>
       </c>
-      <c r="I22" s="2" t="n">
+      <c r="L22" s="2" t="n">
         <v>23</v>
       </c>
     </row>
@@ -1311,17 +1430,24 @@
           <t>October 2011</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Island Records</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>tight fit — may not have aired</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>before first logged spin (20:34)</t>
         </is>
       </c>
-      <c r="I23" s="5" t="n">
+      <c r="L23" s="5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1352,17 +1478,24 @@
           <t>2001</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Peacefrog Records</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>log gap 20:34–20:45 (12 min)</t>
         </is>
       </c>
-      <c r="I24" s="2" t="n">
+      <c r="L24" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1393,17 +1526,24 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>log gap 21:31–21:46 (15 min)</t>
         </is>
       </c>
-      <c r="I25" s="2" t="n">
+      <c r="L25" s="2" t="n">
         <v>16</v>
       </c>
     </row>
@@ -1434,17 +1574,24 @@
           <t>1995</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Spotted Peccary Music</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>log gap 21:31–21:46 (15 min)</t>
         </is>
       </c>
-      <c r="I26" s="2" t="n">
+      <c r="L26" s="2" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1475,17 +1622,24 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Past Inside The Present</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>log gap 21:59–22:12 (13 min)</t>
         </is>
       </c>
-      <c r="I27" s="2" t="n">
+      <c r="L27" s="2" t="n">
         <v>22</v>
       </c>
     </row>
@@ -1516,17 +1670,24 @@
           <t>1985</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Private Music</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>tight fit — may not have aired</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="K28" s="5" t="inlineStr">
         <is>
           <t>after last logged spin (22:20)</t>
         </is>
       </c>
-      <c r="I28" s="5" t="n">
+      <c r="L28" s="5" t="n">
         <v>25</v>
       </c>
     </row>
@@ -1547,25 +1708,34 @@
           <t>Cello Improvisation</t>
         </is>
       </c>
-      <c r="E29" s="5" t="n">
-        <v/>
-      </c>
+      <c r="E29" s="5" t="n"/>
       <c r="F29" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>tight fit — may not have aired</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="K29" s="5" t="inlineStr">
         <is>
           <t>after last logged spin (22:20)</t>
         </is>
       </c>
-      <c r="I29" s="5" t="n">
+      <c r="L29" s="5" t="n">
         <v>26</v>
       </c>
     </row>
@@ -1600,17 +1770,24 @@
           <t>2007</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Flow Records</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>log gap 20:59–21:12 (13 min)</t>
         </is>
       </c>
-      <c r="I30" s="2" t="n">
+      <c r="L30" s="2" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1641,17 +1818,24 @@
           <t>2012</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Black Hole Recordings</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>log gap 21:12–21:26 (14 min)</t>
         </is>
       </c>
-      <c r="I31" s="2" t="n">
+      <c r="L31" s="2" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1682,17 +1866,28 @@
           <t>1989</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Self-Released?</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>tight fit — may not have aired</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t>log gap 21:26–21:34 (8 min)</t>
         </is>
       </c>
-      <c r="I32" s="5" t="n">
+      <c r="L32" s="5" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1723,17 +1918,24 @@
           <t>2013</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>City Slang Records</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>log gap 21:38–21:53 (15 min)</t>
         </is>
       </c>
-      <c r="I33" s="2" t="n">
+      <c r="L33" s="2" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1764,17 +1966,24 @@
           <t>October 2024</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Neotantra</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>log gap 21:53–22:09 (15 min)</t>
         </is>
       </c>
-      <c r="I34" s="2" t="n">
+      <c r="L34" s="2" t="n">
         <v>19</v>
       </c>
     </row>
@@ -1805,17 +2014,24 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Bathysphere Records</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>log gap 21:53–22:09 (15 min)</t>
         </is>
       </c>
-      <c r="I35" s="2" t="n">
+      <c r="L35" s="2" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1846,17 +2062,24 @@
           <t>1972</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Pilz</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>after last logged spin (22:19)</t>
         </is>
       </c>
-      <c r="I36" s="2" t="n">
+      <c r="L36" s="2" t="n">
         <v>24</v>
       </c>
     </row>
@@ -1891,17 +2114,24 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Republic Records</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>tight fit — may not have aired</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="K37" s="5" t="inlineStr">
         <is>
           <t>before first logged spin (20:34)</t>
         </is>
       </c>
-      <c r="I37" s="5" t="n">
+      <c r="L37" s="5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1932,17 +2162,24 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>log gap 20:43–20:57 (14 min)</t>
         </is>
       </c>
-      <c r="I38" s="2" t="n">
+      <c r="L38" s="2" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1973,17 +2210,24 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
         <is>
           <t>log gap 21:16–21:26 (10 min)</t>
         </is>
       </c>
-      <c r="I39" s="2" t="n">
+      <c r="L39" s="2" t="n">
         <v>13</v>
       </c>
     </row>
@@ -2014,17 +2258,28 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2:54</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>INNI</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>log gap 21:46–22:13 (27 min)</t>
         </is>
       </c>
-      <c r="I40" s="2" t="n">
+      <c r="L40" s="2" t="n">
         <v>19</v>
       </c>
     </row>
@@ -2055,17 +2310,24 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Deutsche Grammophon</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
         <is>
           <t>log gap 21:46–22:13 (27 min)</t>
         </is>
       </c>
-      <c r="I41" s="2" t="n">
+      <c r="L41" s="2" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2096,17 +2358,24 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Self-Released</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>log gap 21:46–22:13 (27 min)</t>
         </is>
       </c>
-      <c r="I42" s="2" t="n">
+      <c r="L42" s="2" t="n">
         <v>21</v>
       </c>
     </row>
@@ -2137,17 +2406,24 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Synphaera</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
         <is>
           <t>log gap 21:46–22:13 (27 min)</t>
         </is>
       </c>
-      <c r="I43" s="2" t="n">
+      <c r="L43" s="2" t="n">
         <v>22</v>
       </c>
     </row>
@@ -2178,17 +2454,24 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>World Of Echo Music</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
         <is>
           <t>tight fit — may not have aired</t>
         </is>
       </c>
-      <c r="H44" s="5" t="inlineStr">
+      <c r="K44" s="5" t="inlineStr">
         <is>
           <t>log gap 22:13–22:20 (8 min)</t>
         </is>
       </c>
-      <c r="I44" s="5" t="n">
+      <c r="L44" s="5" t="n">
         <v>24</v>
       </c>
     </row>
@@ -2223,17 +2506,24 @@
           <t>July 2025</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Self-Released</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
         <is>
           <t>log gap 20:40–20:54 (14 min)</t>
         </is>
       </c>
-      <c r="I45" s="2" t="n">
+      <c r="L45" s="2" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2264,17 +2554,24 @@
           <t>1990</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4AD</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>log gap 20:40–20:54 (14 min)</t>
         </is>
       </c>
-      <c r="I46" s="2" t="n">
+      <c r="L46" s="2" t="n">
         <v>8</v>
       </c>
     </row>
@@ -2305,17 +2602,24 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>BBE Music</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
         <is>
           <t>log gap 21:21–21:35 (14 min)</t>
         </is>
       </c>
-      <c r="I47" s="2" t="n">
+      <c r="L47" s="2" t="n">
         <v>15</v>
       </c>
     </row>
@@ -2346,17 +2650,24 @@
           <t>2023 (Reissue)</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>4AD Records</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>log gap 21:53–22:03 (10 min)</t>
         </is>
       </c>
-      <c r="I48" s="2" t="n">
+      <c r="L48" s="2" t="n">
         <v>20</v>
       </c>
     </row>
@@ -2387,17 +2698,28 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Seattle Indies</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
         <is>
           <t>log gap 22:03–22:12 (9 min)</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
+      <c r="L49" s="2" t="n">
         <v>22</v>
       </c>
     </row>
@@ -2428,17 +2750,28 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Self-Released</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
         <is>
           <t>log gap 22:12–22:21 (9 min)</t>
         </is>
       </c>
-      <c r="I50" s="2" t="n">
+      <c r="L50" s="2" t="n">
         <v>24</v>
       </c>
     </row>
@@ -2473,17 +2806,24 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Dogs Got A Bone Records</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
         <is>
           <t>log gap 20:31–20:42 (11 min)</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
+      <c r="L51" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2514,17 +2854,28 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Restless Planet</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
         <is>
           <t>log gap 21:42–21:55 (13 min)</t>
         </is>
       </c>
-      <c r="I52" s="2" t="n">
+      <c r="L52" s="2" t="n">
         <v>18</v>
       </c>
     </row>
@@ -2549,23 +2900,30 @@
           <t>The Louder You Scream</t>
         </is>
       </c>
-      <c r="E53" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F53" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="E53" s="2" t="n"/>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Electronic Sound Magazine</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
         <is>
           <t>log gap 20:42–20:53 (12 min)</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n">
+      <c r="L53" s="2" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2586,23 +2944,30 @@
           <t>Caméléon</t>
         </is>
       </c>
-      <c r="E54" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F54" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="E54" s="2" t="n"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2xHD</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
         <is>
           <t>log gap 21:55–22:06 (11 min)</t>
         </is>
       </c>
-      <c r="I54" s="2" t="n">
+      <c r="L54" s="2" t="n">
         <v>21</v>
       </c>
     </row>
@@ -2623,23 +2988,30 @@
           <t>Me And My Dog</t>
         </is>
       </c>
-      <c r="E55" s="5" t="n">
-        <v/>
-      </c>
-      <c r="F55" s="5" t="n">
-        <v/>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Matador Records</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
         <is>
           <t>tight fit — may not have aired</t>
         </is>
       </c>
-      <c r="H55" s="5" t="inlineStr">
+      <c r="K55" s="5" t="inlineStr">
         <is>
           <t>log gap 22:09–22:17 (8 min)</t>
         </is>
       </c>
-      <c r="I55" s="5" t="n">
+      <c r="L55" s="5" t="n">
         <v>24</v>
       </c>
     </row>
@@ -2674,17 +3046,24 @@
           <t>Self-Released: 2020</t>
         </is>
       </c>
-      <c r="G56" s="5" t="inlineStr">
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Nettwerk</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
         <is>
           <t>tight fit — may not have aired</t>
         </is>
       </c>
-      <c r="H56" s="5" t="inlineStr">
+      <c r="K56" s="5" t="inlineStr">
         <is>
           <t>before first logged spin (20:34)</t>
         </is>
       </c>
-      <c r="I56" s="5" t="n">
+      <c r="L56" s="5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2715,17 +3094,28 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>SecondNature</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
         <is>
           <t>log gap 20:53–21:05 (12 min)</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
+      <c r="L57" s="2" t="n">
         <v>9</v>
       </c>
     </row>
@@ -2756,17 +3146,24 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Self-Released</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
         <is>
           <t>log gap 21:20–21:32 (12 min)</t>
         </is>
       </c>
-      <c r="I58" s="2" t="n">
+      <c r="L58" s="2" t="n">
         <v>15</v>
       </c>
     </row>
@@ -2797,17 +3194,28 @@
           <t>2008</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Bluetech</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
         <is>
           <t>log gap 21:36–21:53 (16 min)</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
+      <c r="L59" s="2" t="n">
         <v>18</v>
       </c>
     </row>
@@ -2838,17 +3246,28 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Self-Released</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
         <is>
           <t>log gap 22:02–22:11 (9 min)</t>
         </is>
       </c>
-      <c r="I60" s="2" t="n">
+      <c r="L60" s="2" t="n">
         <v>22</v>
       </c>
     </row>
@@ -2879,17 +3298,24 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Projekt Records</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
         <is>
           <t>after last logged spin (22:14)</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
+      <c r="L61" s="2" t="n">
         <v>25</v>
       </c>
     </row>
@@ -2924,17 +3350,24 @@
           <t>2012</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Close Up Records</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
         <is>
           <t>log gap 21:00–21:09 (8 min)</t>
         </is>
       </c>
-      <c r="I62" s="2" t="n">
+      <c r="L62" s="2" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2969,17 +3402,24 @@
           <t>2016</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>The Reverberation Appreciation Society</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
         <is>
           <t>log gap 21:32–21:43 (11 min)</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n">
+      <c r="L63" s="2" t="n">
         <v>18</v>
       </c>
     </row>
@@ -3010,17 +3450,28 @@
           <t>April 2024</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Self-Released</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
         <is>
           <t>log gap 22:02–22:13 (11 min)</t>
         </is>
       </c>
-      <c r="I64" s="2" t="n">
+      <c r="L64" s="2" t="n">
         <v>24</v>
       </c>
     </row>
@@ -3055,17 +3506,24 @@
           <t>May 1971</t>
         </is>
       </c>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Tamla</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
         <is>
           <t>tight fit — may not have aired</t>
         </is>
       </c>
-      <c r="H65" s="5" t="inlineStr">
+      <c r="K65" s="5" t="inlineStr">
         <is>
           <t>before first logged spin (20:36)</t>
         </is>
       </c>
-      <c r="I65" s="5" t="n">
+      <c r="L65" s="5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3096,17 +3554,24 @@
           <t>1986</t>
         </is>
       </c>
-      <c r="G66" s="5" t="inlineStr">
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>EMI</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
         <is>
           <t>tight fit — may not have aired</t>
         </is>
       </c>
-      <c r="H66" s="5" t="inlineStr">
+      <c r="K66" s="5" t="inlineStr">
         <is>
           <t>before first logged spin (20:36)</t>
         </is>
       </c>
-      <c r="I66" s="5" t="n">
+      <c r="L66" s="5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3127,23 +3592,26 @@
           <t>Prayers for Rain (Cure Cover)</t>
         </is>
       </c>
-      <c r="E67" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F67" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="E67" s="2" t="n"/>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Dead Vibrations Productions</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
         <is>
           <t>log gap 21:15–21:38 (23 min)</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n">
+      <c r="L67" s="2" t="n">
         <v>14</v>
       </c>
     </row>
@@ -3174,17 +3642,28 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Vief Records</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
         <is>
           <t>log gap 21:15–21:38 (23 min)</t>
         </is>
       </c>
-      <c r="I68" s="2" t="n">
+      <c r="L68" s="2" t="n">
         <v>15</v>
       </c>
     </row>
@@ -3215,17 +3694,24 @@
           <t>October 2025</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Cosmic Signatures</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
         <is>
           <t>log gap 21:15–21:38 (23 min)</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n">
+      <c r="L69" s="2" t="n">
         <v>16</v>
       </c>
     </row>
@@ -3256,17 +3742,28 @@
           <t>September 2016</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Hotham Sound</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
         <is>
           <t>log gap 21:15–21:38 (23 min)</t>
         </is>
       </c>
-      <c r="I70" s="2" t="n">
+      <c r="L70" s="2" t="n">
         <v>17</v>
       </c>
     </row>
@@ -3301,17 +3798,24 @@
           <t>December 1989</t>
         </is>
       </c>
-      <c r="G71" s="5" t="inlineStr">
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Beggars Banquet</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
         <is>
           <t>tight fit — may not have aired</t>
         </is>
       </c>
-      <c r="H71" s="5" t="inlineStr">
+      <c r="K71" s="5" t="inlineStr">
         <is>
           <t>before first logged spin (20:33)</t>
         </is>
       </c>
-      <c r="I71" s="5" t="n">
+      <c r="L71" s="5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3342,17 +3846,28 @@
           <t>March 2020</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>SFI Recordings</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
         <is>
           <t>log gap 20:41–20:49 (8 min)</t>
         </is>
       </c>
-      <c r="I72" s="2" t="n">
+      <c r="L72" s="2" t="n">
         <v>7</v>
       </c>
     </row>
@@ -3383,17 +3898,28 @@
           <t>September 2025</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Self Released</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
         <is>
           <t>log gap 21:29–21:37 (8 min)</t>
         </is>
       </c>
-      <c r="I73" s="2" t="n">
+      <c r="L73" s="2" t="n">
         <v>19</v>
       </c>
     </row>
@@ -3424,17 +3950,28 @@
           <t>July 2025</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Self Released (by Fred's Daughter)</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
         <is>
           <t>after last logged spin (22:16)</t>
         </is>
       </c>
-      <c r="I74" s="2" t="n">
+      <c r="L74" s="2" t="n">
         <v>29</v>
       </c>
     </row>
@@ -3469,17 +4006,28 @@
           <t>February 2021</t>
         </is>
       </c>
-      <c r="G75" s="5" t="inlineStr">
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Self Released</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
         <is>
           <t>tight fit — may not have aired</t>
         </is>
       </c>
-      <c r="H75" s="5" t="inlineStr">
+      <c r="K75" s="5" t="inlineStr">
         <is>
           <t>before first logged spin (20:32)</t>
         </is>
       </c>
-      <c r="I75" s="5" t="n">
+      <c r="L75" s="5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3510,17 +4058,24 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Columbia</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
         <is>
           <t>log gap 20:32–20:40 (8 min)</t>
         </is>
       </c>
-      <c r="I76" s="2" t="n">
+      <c r="L76" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3551,17 +4106,28 @@
           <t>July 2020</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Self Released</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
         <is>
           <t>log gap 21:33–21:44 (12 min)</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
+      <c r="L77" s="2" t="n">
         <v>18</v>
       </c>
     </row>
@@ -3592,17 +4158,24 @@
           <t>Released in 2009</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Doombient Music</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
         <is>
           <t>log gap 21:49–21:59 (10 min)</t>
         </is>
       </c>
-      <c r="I78" s="2" t="n">
+      <c r="L78" s="2" t="n">
         <v>21</v>
       </c>
     </row>
@@ -3633,17 +4206,28 @@
           <t>August 2024</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Self Released</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
         <is>
           <t>log gap 21:59–22:16 (17 min)</t>
         </is>
       </c>
-      <c r="I79" s="2" t="n">
+      <c r="L79" s="2" t="n">
         <v>23</v>
       </c>
     </row>
@@ -3674,17 +4258,28 @@
           <t>May 2012</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Kinnta (Montreal based label)</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
         <is>
           <t>log gap 21:59–22:16 (17 min)</t>
         </is>
       </c>
-      <c r="I80" s="2" t="n">
+      <c r="L80" s="2" t="n">
         <v>24</v>
       </c>
     </row>
@@ -3719,17 +4314,24 @@
           <t>March 1986</t>
         </is>
       </c>
-      <c r="G81" s="5" t="inlineStr">
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Sire Records (in US)</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
         <is>
           <t>tight fit — may not have aired</t>
         </is>
       </c>
-      <c r="H81" s="5" t="inlineStr">
+      <c r="K81" s="5" t="inlineStr">
         <is>
           <t>before first logged spin (20:36)</t>
         </is>
       </c>
-      <c r="I81" s="5" t="n">
+      <c r="L81" s="5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3760,17 +4362,28 @@
           <t>Single to be released December 12, 2025</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Presumably Ghost Mountain Records (as with past releases).</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
         <is>
           <t>log gap 20:41–20:51 (10 min)</t>
         </is>
       </c>
-      <c r="I82" s="2" t="n">
+      <c r="L82" s="2" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3801,17 +4414,24 @@
           <t>March 2024</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
         <is>
           <t>log gap 21:07–21:19 (13 min)</t>
         </is>
       </c>
-      <c r="I83" s="2" t="n">
+      <c r="L83" s="2" t="n">
         <v>12</v>
       </c>
     </row>
@@ -3842,17 +4462,24 @@
           <t>July 2025</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
         <is>
           <t>log gap 21:24–21:33 (9 min)</t>
         </is>
       </c>
-      <c r="I84" s="2" t="n">
+      <c r="L84" s="2" t="n">
         <v>15</v>
       </c>
     </row>
@@ -3883,17 +4510,24 @@
           <t>2012</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Sacred Bones Records</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
         <is>
           <t>log gap 21:36–21:45 (9 min)</t>
         </is>
       </c>
-      <c r="I85" s="2" t="n">
+      <c r="L85" s="2" t="n">
         <v>18</v>
       </c>
     </row>
@@ -3924,17 +4558,32 @@
           <t>June 2017</t>
         </is>
       </c>
-      <c r="G86" s="5" t="inlineStr">
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>4:53</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Kylmyys Kollective</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="inlineStr">
         <is>
           <t>tight fit — may not have aired</t>
         </is>
       </c>
-      <c r="H86" s="5" t="inlineStr">
+      <c r="K86" s="5" t="inlineStr">
         <is>
           <t>after last logged spin (22:24)</t>
         </is>
       </c>
-      <c r="I86" s="5" t="n">
+      <c r="L86" s="5" t="n">
         <v>27</v>
       </c>
     </row>
@@ -3969,17 +4618,24 @@
           <t>January 2014</t>
         </is>
       </c>
-      <c r="G87" s="5" t="inlineStr">
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Naked Music Recordings</t>
+        </is>
+      </c>
+      <c r="J87" s="5" t="inlineStr">
         <is>
           <t>tight fit — may not have aired</t>
         </is>
       </c>
-      <c r="H87" s="5" t="inlineStr">
+      <c r="K87" s="5" t="inlineStr">
         <is>
           <t>log gap 21:24–21:30 (6 min)</t>
         </is>
       </c>
-      <c r="I87" s="5" t="n">
+      <c r="L87" s="5" t="n">
         <v>14</v>
       </c>
     </row>
@@ -4010,17 +4666,28 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Self Released</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
         <is>
           <t>log gap 21:34–21:53 (19 min)</t>
         </is>
       </c>
-      <c r="I88" s="2" t="n">
+      <c r="L88" s="2" t="n">
         <v>17</v>
       </c>
     </row>
@@ -4051,17 +4718,24 @@
           <t>October 2020</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Counter Records</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
         <is>
           <t>log gap 21:34–21:53 (19 min)</t>
         </is>
       </c>
-      <c r="I89" s="2" t="n">
+      <c r="L89" s="2" t="n">
         <v>18</v>
       </c>
     </row>
@@ -4092,17 +4766,28 @@
           <t>August 2025</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Self Released</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
         <is>
           <t>log gap 22:08–22:20 (12 min)</t>
         </is>
       </c>
-      <c r="I90" s="2" t="n">
+      <c r="L90" s="2" t="n">
         <v>23</v>
       </c>
     </row>
@@ -4140,17 +4825,20 @@
           <t>June 2025</t>
         </is>
       </c>
-      <c r="G91" s="5" t="inlineStr">
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" s="5" t="inlineStr">
         <is>
           <t>tight fit — may not have aired</t>
         </is>
       </c>
-      <c r="H91" s="5" t="inlineStr">
+      <c r="K91" s="5" t="inlineStr">
         <is>
           <t>before first logged spin (20:37)</t>
         </is>
       </c>
-      <c r="I91" s="5" t="n">
+      <c r="L91" s="5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4181,17 +4869,28 @@
           <t>February 2022</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>SecondNature</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
         <is>
           <t>log gap 21:01–21:13 (12 min)</t>
         </is>
       </c>
-      <c r="I92" s="2" t="n">
+      <c r="L92" s="2" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4222,17 +4921,28 @@
           <t>March 2023</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>SecondNature</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
         <is>
           <t>log gap 21:24–21:37 (13 min)</t>
         </is>
       </c>
-      <c r="I93" s="2" t="n">
+      <c r="L93" s="2" t="n">
         <v>14</v>
       </c>
     </row>
@@ -4263,17 +4973,28 @@
           <t>August 2024</t>
         </is>
       </c>
-      <c r="G94" s="5" t="inlineStr">
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Self-Released</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="inlineStr">
         <is>
           <t>tight fit — may not have aired</t>
         </is>
       </c>
-      <c r="H94" s="5" t="inlineStr">
+      <c r="K94" s="5" t="inlineStr">
         <is>
           <t>log gap 21:56–22:02 (6 min)</t>
         </is>
       </c>
-      <c r="I94" s="5" t="n">
+      <c r="L94" s="5" t="n">
         <v>19</v>
       </c>
     </row>
@@ -4308,17 +5029,24 @@
           <t>May 2020</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Steeplejack Rec</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
         <is>
           <t>log gap 20:51–21:02 (11 min)</t>
         </is>
       </c>
-      <c r="I95" s="2" t="n">
+      <c r="L95" s="2" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4349,17 +5077,28 @@
           <t>August 2025</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Self Released</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
         <is>
           <t>log gap 21:20–21:32 (12 min)</t>
         </is>
       </c>
-      <c r="I96" s="2" t="n">
+      <c r="L96" s="2" t="n">
         <v>15</v>
       </c>
     </row>
@@ -4390,17 +5129,28 @@
           <t>January 2026</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Self-Released</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
         <is>
           <t>log gap 22:01–22:10 (9 min)</t>
         </is>
       </c>
-      <c r="I97" s="2" t="n">
+      <c r="L97" s="2" t="n">
         <v>23</v>
       </c>
     </row>
@@ -4431,17 +5181,28 @@
           <t>November 2024</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Kelp Roots</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
         <is>
           <t>after last logged spin (22:17)</t>
         </is>
       </c>
-      <c r="I98" s="2" t="n">
+      <c r="L98" s="2" t="n">
         <v>27</v>
       </c>
     </row>
@@ -4476,17 +5237,24 @@
           <t>May 2017</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Self Released</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
         <is>
           <t>log gap 20:55–21:06 (11 min)</t>
         </is>
       </c>
-      <c r="I99" s="2" t="n">
+      <c r="L99" s="2" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4517,17 +5285,28 @@
           <t>April 2020</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Second Nature</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
         <is>
           <t>log gap 21:28–21:39 (11 min)</t>
         </is>
       </c>
-      <c r="I100" s="2" t="n">
+      <c r="L100" s="2" t="n">
         <v>14</v>
       </c>
     </row>
@@ -4558,17 +5337,28 @@
           <t>March 2017</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Second Nature</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
         <is>
           <t>log gap 21:44–21:58 (14 min)</t>
         </is>
       </c>
-      <c r="I101" s="2" t="n">
+      <c r="L101" s="2" t="n">
         <v>17</v>
       </c>
     </row>
@@ -4603,17 +5393,28 @@
           <t>March 13, 2026</t>
         </is>
       </c>
-      <c r="G102" s="5" t="inlineStr">
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Self-Released</t>
+        </is>
+      </c>
+      <c r="J102" s="5" t="inlineStr">
         <is>
           <t>tight fit — may not have aired</t>
         </is>
       </c>
-      <c r="H102" s="5" t="inlineStr">
+      <c r="K102" s="5" t="inlineStr">
         <is>
           <t>before first logged spin (20:32)</t>
         </is>
       </c>
-      <c r="I102" s="5" t="n">
+      <c r="L102" s="5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4644,17 +5445,24 @@
           <t>September 2016</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>SecondNature</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
         <is>
           <t>log gap 21:25–21:38 (12 min)</t>
         </is>
       </c>
-      <c r="I103" s="2" t="n">
+      <c r="L103" s="2" t="n">
         <v>15</v>
       </c>
     </row>
@@ -4685,17 +5493,24 @@
           <t>September 2001</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Jumpin' &amp; Pumpin'</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
         <is>
           <t>log gap 21:25–21:38 (12 min)</t>
         </is>
       </c>
-      <c r="I104" s="2" t="n">
+      <c r="L104" s="2" t="n">
         <v>16</v>
       </c>
     </row>
@@ -4726,17 +5541,20 @@
           <t>December 2012</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
         <is>
           <t>after last logged spin (22:17)</t>
         </is>
       </c>
-      <c r="I105" s="2" t="n">
+      <c r="L105" s="2" t="n">
         <v>25</v>
       </c>
     </row>
@@ -4767,17 +5585,28 @@
           <t>January 2026</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Self-Released</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
         <is>
           <t>after last logged spin (22:17)</t>
         </is>
       </c>
-      <c r="I106" s="2" t="n">
+      <c r="L106" s="2" t="n">
         <v>26</v>
       </c>
     </row>
@@ -4812,17 +5641,24 @@
           <t>1999</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Xtravaganza Recordings</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
         <is>
           <t>log gap 20:35–21:00 (25 min)</t>
         </is>
       </c>
-      <c r="I107" s="2" t="n">
+      <c r="L107" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4853,17 +5689,24 @@
           <t>2003</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Artista</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
         <is>
           <t>log gap 20:35–21:00 (25 min)</t>
         </is>
       </c>
-      <c r="I108" s="2" t="n">
+      <c r="L108" s="2" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4894,17 +5737,28 @@
           <t>December 2025</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Self Released</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
         <is>
           <t>log gap 20:35–21:00 (25 min)</t>
         </is>
       </c>
-      <c r="I109" s="2" t="n">
+      <c r="L109" s="2" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4935,17 +5789,28 @@
           <t>November 2025</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Self-Released</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
         <is>
           <t>log gap 20:35–21:00 (25 min)</t>
         </is>
       </c>
-      <c r="I110" s="2" t="n">
+      <c r="L110" s="2" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4976,17 +5841,24 @@
           <t>December 2025</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Self-Released</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
         <is>
           <t>log gap 21:00–21:10 (10 min)</t>
         </is>
       </c>
-      <c r="I111" s="2" t="n">
+      <c r="L111" s="2" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5017,17 +5889,28 @@
           <t>March 2026</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Self-Released</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
         <is>
           <t>log gap 21:23–21:42 (19 min)</t>
         </is>
       </c>
-      <c r="I112" s="2" t="n">
+      <c r="L112" s="2" t="n">
         <v>15</v>
       </c>
     </row>
@@ -5058,17 +5941,24 @@
           <t>December 2016</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Self-Released</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
         <is>
           <t>log gap 21:23–21:42 (19 min)</t>
         </is>
       </c>
-      <c r="I113" s="2" t="n">
+      <c r="L113" s="2" t="n">
         <v>16</v>
       </c>
     </row>
@@ -5099,17 +5989,28 @@
           <t>February 2026</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Onset Audio (Seattle)</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
         <is>
           <t>log gap 21:23–21:42 (19 min)</t>
         </is>
       </c>
-      <c r="I114" s="2" t="n">
+      <c r="L114" s="2" t="n">
         <v>17</v>
       </c>
     </row>
@@ -5140,17 +6041,28 @@
           <t>March 2026</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Self-Released</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
         <is>
           <t>log gap 22:04–22:13 (9 min)</t>
         </is>
       </c>
-      <c r="I115" s="2" t="n">
+      <c r="L115" s="2" t="n">
         <v>23</v>
       </c>
     </row>
@@ -5185,17 +6097,24 @@
           <t>April 2026</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Brainfeeder</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
         <is>
           <t>log gap 21:01–21:10 (9 min)</t>
         </is>
       </c>
-      <c r="I116" s="2" t="n">
+      <c r="L116" s="2" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5226,17 +6145,28 @@
           <t>July 2024</t>
         </is>
       </c>
-      <c r="G117" s="5" t="inlineStr">
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Wax Thematique</t>
+        </is>
+      </c>
+      <c r="J117" s="5" t="inlineStr">
         <is>
           <t>tight fit — may not have aired</t>
         </is>
       </c>
-      <c r="H117" s="5" t="inlineStr">
+      <c r="K117" s="5" t="inlineStr">
         <is>
           <t>log gap 21:10–21:22 (12 min)</t>
         </is>
       </c>
-      <c r="I117" s="5" t="n">
+      <c r="L117" s="5" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5267,17 +6197,28 @@
           <t>April, 2026</t>
         </is>
       </c>
-      <c r="G118" s="5" t="inlineStr">
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Self Released</t>
+        </is>
+      </c>
+      <c r="J118" s="5" t="inlineStr">
         <is>
           <t>tight fit — may not have aired</t>
         </is>
       </c>
-      <c r="H118" s="5" t="inlineStr">
+      <c r="K118" s="5" t="inlineStr">
         <is>
           <t>log gap 21:10–21:22 (12 min)</t>
         </is>
       </c>
-      <c r="I118" s="5" t="n">
+      <c r="L118" s="5" t="n">
         <v>13</v>
       </c>
     </row>
@@ -5308,17 +6249,20 @@
           <t>February 2026</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
         <is>
           <t>after last logged spin (22:05)</t>
         </is>
       </c>
-      <c r="I119" s="2" t="n">
+      <c r="L119" s="2" t="n">
         <v>26</v>
       </c>
     </row>
@@ -5349,17 +6293,28 @@
           <t>December 2025</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Behind The Sky Music</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
         <is>
           <t>after last logged spin (22:05)</t>
         </is>
       </c>
-      <c r="I120" s="2" t="n">
+      <c r="L120" s="2" t="n">
         <v>27</v>
       </c>
     </row>
@@ -5394,17 +6349,20 @@
           <t>May 2026</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
         <is>
           <t>log gap 21:00–21:13 (13 min)</t>
         </is>
       </c>
-      <c r="I121" s="2" t="n">
+      <c r="L121" s="2" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5435,17 +6393,28 @@
           <t>February 2026</t>
         </is>
       </c>
-      <c r="G122" s="5" t="inlineStr">
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Self-Released (?)</t>
+        </is>
+      </c>
+      <c r="J122" s="5" t="inlineStr">
         <is>
           <t>tight fit — may not have aired</t>
         </is>
       </c>
-      <c r="H122" s="5" t="inlineStr">
+      <c r="K122" s="5" t="inlineStr">
         <is>
           <t>log gap 21:37–21:44 (8 min)</t>
         </is>
       </c>
-      <c r="I122" s="5" t="n">
+      <c r="L122" s="5" t="n">
         <v>18</v>
       </c>
     </row>
@@ -5476,17 +6445,28 @@
           <t>April 2026</t>
         </is>
       </c>
-      <c r="G123" s="5" t="inlineStr">
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Self-Released (?)</t>
+        </is>
+      </c>
+      <c r="J123" s="5" t="inlineStr">
         <is>
           <t>tight fit — may not have aired</t>
         </is>
       </c>
-      <c r="H123" s="5" t="inlineStr">
+      <c r="K123" s="5" t="inlineStr">
         <is>
           <t>log gap 21:47–21:52 (5 min)</t>
         </is>
       </c>
-      <c r="I123" s="5" t="n">
+      <c r="L123" s="5" t="n">
         <v>21</v>
       </c>
     </row>
@@ -5517,17 +6497,28 @@
           <t>September 2025</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Self-Released (?)</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
         <is>
           <t>log gap 22:03–22:17 (14 min)</t>
         </is>
       </c>
-      <c r="I124" s="2" t="n">
+      <c r="L124" s="2" t="n">
         <v>25</v>
       </c>
     </row>
@@ -5558,17 +6549,28 @@
           <t>April 2026</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Self-Released (?)</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
         <is>
           <t>log gap 22:03–22:17 (14 min)</t>
         </is>
       </c>
-      <c r="I125" s="2" t="n">
+      <c r="L125" s="2" t="n">
         <v>26</v>
       </c>
     </row>
@@ -5599,17 +6601,28 @@
           <t>February 2026</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Self Released</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
         <is>
           <t>after last logged spin (22:17)</t>
         </is>
       </c>
-      <c r="I126" s="2" t="n">
+      <c r="L126" s="2" t="n">
         <v>28</v>
       </c>
     </row>
@@ -5644,17 +6657,28 @@
           <t>April 10, 2026</t>
         </is>
       </c>
-      <c r="G127" s="5" t="inlineStr">
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Ninety9Lives</t>
+        </is>
+      </c>
+      <c r="J127" s="5" t="inlineStr">
         <is>
           <t>tight fit — may not have aired</t>
         </is>
       </c>
-      <c r="H127" s="5" t="inlineStr">
+      <c r="K127" s="5" t="inlineStr">
         <is>
           <t>before first logged spin (20:42)</t>
         </is>
       </c>
-      <c r="I127" s="5" t="n">
+      <c r="L127" s="5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5685,17 +6709,24 @@
           <t>February 2026</t>
         </is>
       </c>
-      <c r="G128" s="5" t="inlineStr">
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>No Quarter Productions</t>
+        </is>
+      </c>
+      <c r="J128" s="5" t="inlineStr">
         <is>
           <t>tight fit — may not have aired</t>
         </is>
       </c>
-      <c r="H128" s="5" t="inlineStr">
+      <c r="K128" s="5" t="inlineStr">
         <is>
           <t>before first logged spin (20:42)</t>
         </is>
       </c>
-      <c r="I128" s="5" t="n">
+      <c r="L128" s="5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5726,17 +6757,28 @@
           <t>May 17  2026</t>
         </is>
       </c>
-      <c r="G129" s="5" t="inlineStr">
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Self-Released</t>
+        </is>
+      </c>
+      <c r="J129" s="5" t="inlineStr">
         <is>
           <t>tight fit — may not have aired</t>
         </is>
       </c>
-      <c r="H129" s="5" t="inlineStr">
+      <c r="K129" s="5" t="inlineStr">
         <is>
           <t>before first logged spin (20:42)</t>
         </is>
       </c>
-      <c r="I129" s="5" t="n">
+      <c r="L129" s="5" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5767,17 +6809,28 @@
           <t>April 1, 2026</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Self Released</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
         <is>
           <t>log gap 21:33–21:59 (25 min)</t>
         </is>
       </c>
-      <c r="I130" s="2" t="n">
+      <c r="L130" s="2" t="n">
         <v>17</v>
       </c>
     </row>
@@ -5808,17 +6861,32 @@
           <t>May 15, 2026</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>6:38</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Black Hole Recordings</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
         <is>
           <t>log gap 21:33–21:59 (25 min)</t>
         </is>
       </c>
-      <c r="I131" s="2" t="n">
+      <c r="L131" s="2" t="n">
         <v>18</v>
       </c>
     </row>
@@ -5849,17 +6917,28 @@
           <t>May 10, 2026</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Self-Released</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
         <is>
           <t>log gap 21:33–21:59 (25 min)</t>
         </is>
       </c>
-      <c r="I132" s="2" t="n">
+      <c r="L132" s="2" t="n">
         <v>19</v>
       </c>
     </row>
@@ -5890,17 +6969,28 @@
           <t>May 15, 2026</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Heavy Sounds (Seattle)</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
         <is>
           <t>log gap 21:33–21:59 (25 min)</t>
         </is>
       </c>
-      <c r="I133" s="2" t="n">
+      <c r="L133" s="2" t="n">
         <v>20</v>
       </c>
     </row>
@@ -5931,17 +7021,24 @@
           <t>July 31, 2026</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t>likely aired</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Self-Released</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>likely aired</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
         <is>
           <t>log gap 21:59–22:10 (11 min)</t>
         </is>
       </c>
-      <c r="I134" s="2" t="n">
+      <c r="L134" s="2" t="n">
         <v>22</v>
       </c>
     </row>
@@ -5957,7 +7054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6005,10 +7102,30 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
+          <t>Album</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Release</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>Possible replacement</t>
         </is>
@@ -6040,7 +7157,23 @@
           <t>Day And Night</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>5:13</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Sleepingroom Musik</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -6068,7 +7201,23 @@
           <t>White Winds (Seeker's Journey)</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>3:02</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>AVAF Music</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>may actually be: Rubaja And Hernandez — Forest</t>
         </is>
@@ -6096,7 +7245,23 @@
           <t>Odonata</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4:21</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Neurodisc Records</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>may actually be: Active Dark Filament — The Glow of Distant Lights</t>
         </is>
@@ -6124,7 +7289,23 @@
           <t>iota</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4:31</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Spotted Peccary</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
         <is>
           <t>may actually be: Blank &amp; Jones — Desire (Ambient Album Mix)</t>
         </is>
@@ -6152,7 +7333,23 @@
           <t>Missing You</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>5:55</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Jackin' Social Club</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr"/>
@@ -6176,7 +7373,23 @@
           <t>American Beauty (Soundtrack)</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4:07</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>UMG Recordings, Inc.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr"/>
@@ -6200,7 +7413,23 @@
           <t>Meddle</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>5:56</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Pink Floyd Music Ltd</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -6228,7 +7457,23 @@
           <t>Continuum</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>3:09</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Spotted Peccary</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
         <is>
           <t>may actually be: Haunted Computer — Escape From Beach Drive</t>
         </is>
@@ -6256,7 +7501,23 @@
           <t>Deep Breakfast</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>6:01</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Ray Lynch Productions</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="inlineStr">
         <is>
           <t>may actually be: Nitechord — Near</t>
         </is>
@@ -6288,7 +7549,23 @@
           <t>8 Imaginario</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>3:40</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Quiroga Finest Records</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">may actually be: Popol Vuh  — Hosianna Mantra </t>
         </is>
@@ -6320,7 +7597,23 @@
           <t>Sounds of Summer</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2:54</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>INNI</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>may actually be: Sin Fang, “Jónsi” Birgisson, and Kjartan Holm — Ofbirta (Ohf birta)</t>
         </is>
@@ -6352,7 +7645,23 @@
           <t>Luck and Strange</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1:32</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Legacy Recordings</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr"/>
@@ -6376,7 +7685,15 @@
           <t>Late Night Tales: Trentemøller</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr"/>
@@ -6400,7 +7717,23 @@
           <t>HeatleyBros VI</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>3:20</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Kyzen Music</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
         <is>
           <t>may actually be: DadHatTony — Frightmare</t>
         </is>
@@ -6428,7 +7761,23 @@
           <t>Surrender</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>8:39</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Virgin Records</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -6456,7 +7805,23 @@
           <t>Me &amp; My Dog</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>3:26</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Matador</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
         <is>
           <t>may actually be: Boygenius — Me And My Dog</t>
         </is>
@@ -6488,7 +7853,23 @@
           <t>Freehand</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>3:11</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>OJM</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr">
         <is>
           <t>may actually be: Simic — Saturn</t>
         </is>
@@ -6516,7 +7897,23 @@
           <t>Melodic House &amp; Techno Drum Loops Vol.2</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>5:22</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Danirava Records Samples Area</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
         <is>
           <t>may actually be: yu-more — Organize Before Life</t>
         </is>
@@ -6544,7 +7941,23 @@
           <t>Dreamtime Submersible</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Somnia</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">may actually be: Bluetech and Steve Hillage — Hypnagogue </t>
         </is>
@@ -6572,7 +7985,23 @@
           <t>Atlas</t>
         </is>
       </c>
-      <c r="F24" s="9" t="inlineStr">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>4:16</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Awe</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr">
         <is>
           <t>may actually be: Deepspace — ApproachingTheBlue</t>
         </is>
@@ -6604,7 +8033,23 @@
           <t>Eu Só Volto Com a Vitória</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2:33</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Thiago SKP</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr"/>
@@ -6628,7 +8073,23 @@
           <t>Above the Shore</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>5:14</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Daryl Groetsch</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="inlineStr">
         <is>
           <t>may actually be: Pulse Emitter — Above The Shore</t>
         </is>
@@ -6660,7 +8121,27 @@
           <t>Let Go</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>3:14</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Dayderam Records</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr"/>
@@ -6684,7 +8165,27 @@
           <t>Horizons</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>4:27</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Dismal Nitch</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -6712,7 +8213,23 @@
           <t>The Shining (Selections from the Original Motion Picture Soundtrack)</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>3:24</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>WaterTower Music</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -6740,7 +8257,23 @@
           <t>The Journey (Real World Gold)</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>5:53</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Real World Records</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr"/>
@@ -6764,7 +8297,23 @@
           <t>Nothing Wrong</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr">
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>3:25</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Crosstown Rebels</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="inlineStr">
         <is>
           <t>may actually be: DropLab — OMRI. - Nothing Wrong (Love Mix)</t>
         </is>
@@ -6796,7 +8345,23 @@
           <t>Christmas Party</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1900</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>3:06</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>London-Sire</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr"/>
@@ -6820,7 +8385,23 @@
           <t>Hjerternes fest 2020</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>3:24</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>UMOD (Universal Music On Demand)</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="inlineStr">
         <is>
           <t>may actually be: ramp — The Deep Well</t>
         </is>
@@ -6852,7 +8433,23 @@
           <t>Oculus Omnia</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr">
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>4:01</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Serial Killin Records</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
         <is>
           <t>may actually be: Depeche Mode — Stripped</t>
         </is>
@@ -6880,7 +8477,23 @@
           <t>Christmas Party</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1900</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>3:06</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>London-Sire</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr"/>
@@ -6904,7 +8517,23 @@
           <t>Hjerternes fest 2020</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>3:24</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>UMOD (Universal Music On Demand)</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr"/>
@@ -6928,7 +8557,23 @@
           <t>Dusk</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>4:53</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Kylmyys Kollective</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="inlineStr">
         <is>
           <t>may actually be: Kylmyys (Similar to Kill/Keel Moose…Finnish for Cold) — Pollyanna</t>
         </is>
@@ -6960,7 +8605,27 @@
           <t>There go the Angels</t>
         </is>
       </c>
-      <c r="F38" s="9" t="inlineStr">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>6:08</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Self-Released</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="inlineStr">
         <is>
           <t>may actually be: Bete Grise
 Beht Greeze)
@@ -6995,7 +8660,23 @@
           <t>Surrender</t>
         </is>
       </c>
-      <c r="F39" s="9" t="inlineStr">
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>5:18</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Kwintessens</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="inlineStr">
         <is>
           <t>may actually be: Ola Gjeilo (Ola Yay-Low) — The Spheres (Excerpt: Part 3)</t>
         </is>
@@ -7023,7 +8704,23 @@
           <t>knightfall / juno</t>
         </is>
       </c>
-      <c r="F40" s="9" t="inlineStr">
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>5:46</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>archaea</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="inlineStr">
         <is>
           <t>may actually be: Ola Gjeilo (Ola Yay-Low) — The Spheres (Excerpt: Part 3)</t>
         </is>
@@ -7055,7 +8752,23 @@
           <t>Play Of Color Blue Sound Palette Vol.2 Side B</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>5:29</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Play Of Color Blue</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
@@ -7083,7 +8796,23 @@
           <t>A Series of Actions in a Sphere of Forever</t>
         </is>
       </c>
-      <c r="F42" s="9" t="inlineStr">
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1:42</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Smalltown Supersound</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="inlineStr">
         <is>
           <t>may actually be: Quits — Dowsing</t>
         </is>
@@ -7115,7 +8844,23 @@
           <t>seasons of wither</t>
         </is>
       </c>
-      <c r="F43" s="9" t="inlineStr">
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4:16</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ARCHAEA</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="inlineStr">
         <is>
           <t>may actually be: TERRACE — Avoidant (Personality)</t>
         </is>
@@ -7147,7 +8892,23 @@
           <t>Slide &amp; Joy</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>4:15</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>OJM Records</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="9" t="inlineStr"/>
@@ -7171,7 +8932,23 @@
           <t>Metaversal</t>
         </is>
       </c>
-      <c r="F45" s="9" t="inlineStr">
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>6:38</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Black Hole Recordings</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="inlineStr">
         <is>
           <t>may actually be: Sirendia — The In Between (Remix)</t>
         </is>
